--- a/sampleprojects/TaxReturn/excel/states/NC.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/NC.xlsx
@@ -84,7 +84,7 @@
     <t>MFJ/QSS: deduction $25,500; tax = max(AGI − 25,500, 0) × 4.25%</t>
   </si>
   <si>
-    <t>set result.nc_taxable_income = the maximum of (result.agi - 25500.0) and 0.0; set result.nc_state_tax = result.nc_taxable_income * 0.0425</t>
+    <t>set result.nc_taxable_income = the maximum of (result.state_calc_agi - 25500.0) and 0.0; set result.nc_state_tax = result.nc_taxable_income * 0.0425</t>
   </si>
   <si>
     <t>X</t>
@@ -93,13 +93,13 @@
     <t>HOH: deduction $22,500; tax = max(AGI − 22,500, 0) × 4.25%</t>
   </si>
   <si>
-    <t>set result.nc_taxable_income = the maximum of (result.agi - 22500.0) and 0.0; set result.nc_state_tax = result.nc_taxable_income * 0.0425</t>
+    <t>set result.nc_taxable_income = the maximum of (result.state_calc_agi - 22500.0) and 0.0; set result.nc_state_tax = result.nc_taxable_income * 0.0425</t>
   </si>
   <si>
     <t>Default (Single/MFS): deduction $12,750; tax = max(AGI − 12,750, 0) × 4.25%</t>
   </si>
   <si>
-    <t>set result.nc_taxable_income = the maximum of (result.agi - 12750.0) and 0.0; set result.nc_state_tax = result.nc_taxable_income * 0.0425</t>
+    <t>set result.nc_taxable_income = the maximum of (result.state_calc_agi - 12750.0) and 0.0; set result.nc_state_tax = result.nc_taxable_income * 0.0425</t>
   </si>
   <si>
     <t>Publish state result to the generic computed_state_tax fields</t>
